--- a/artfynd/A 55316-2023 artfynd.xlsx
+++ b/artfynd/A 55316-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 55316-2023 artfynd.xlsx
+++ b/artfynd/A 55316-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY10"/>
+  <dimension ref="A1:AY11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>53319591</v>
+        <v>78057661</v>
       </c>
       <c r="B2" t="n">
-        <v>57073</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,45 +686,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103056</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Videsparv</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Emberiza rustica</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Pallas, 1776</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Kvarnberget, SCA-rågången, Nb</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>800889.3669259243</v>
+        <v>800889</v>
       </c>
       <c r="R2" t="n">
-        <v>7329176.325592783</v>
+        <v>7329176</v>
       </c>
       <c r="S2" t="n">
         <v>50</v>
@@ -756,27 +743,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2015-05-10</t>
+          <t>2019-05-27</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2015-05-10</t>
+          <t>2019-05-27</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>14:00</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>På Buddbymarken.</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -785,6 +767,7 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -803,15 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>53319415</v>
+        <v>71377973</v>
       </c>
       <c r="B3" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -819,33 +797,25 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>1312</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -853,10 +823,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>800889.3669259243</v>
+        <v>800889</v>
       </c>
       <c r="R3" t="n">
-        <v>7329176.325592783</v>
+        <v>7329176</v>
       </c>
       <c r="S3" t="n">
         <v>50</v>
@@ -883,27 +853,27 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2015-05-10</t>
+          <t>2018-05-17</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2015-05-10</t>
+          <t>2018-05-17</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>19:40</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Lunglavar på minst fem sälgar på Buddbymarken några meter från rågången.</t>
+          <t>På en gran.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -912,6 +882,7 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -930,56 +901,49 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>67518931</v>
+        <v>78060043</v>
       </c>
       <c r="B4" t="n">
-        <v>89410</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97231</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5432</v>
+        <v>2869</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>Girg.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Kvarnberget, SCA-rågången, Nb</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>800889.3669259243</v>
+        <v>800889</v>
       </c>
       <c r="R4" t="n">
-        <v>7329176.325592783</v>
+        <v>7329176</v>
       </c>
       <c r="S4" t="n">
         <v>50</v>
@@ -1006,27 +970,27 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2017-09-11</t>
+          <t>2019-05-27</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2017-09-11</t>
+          <t>2019-05-27</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>På en gran vid rågången.</t>
+          <t>Spridd förekomst.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1054,15 +1018,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>71377973</v>
+        <v>53319415</v>
       </c>
       <c r="B5" t="n">
-        <v>81236</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1070,25 +1029,33 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1312</v>
+        <v>6458</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1096,10 +1063,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>800889.3669259243</v>
+        <v>800889</v>
       </c>
       <c r="R5" t="n">
-        <v>7329176.325592783</v>
+        <v>7329176</v>
       </c>
       <c r="S5" t="n">
         <v>50</v>
@@ -1126,27 +1093,27 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2018-05-17</t>
+          <t>2015-05-10</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2018-05-17</t>
+          <t>2015-05-10</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>19:40</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>På en gran.</t>
+          <t>Lunglavar på minst fem sälgar på Buddbymarken några meter från rågången.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1155,7 +1122,6 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1174,64 +1140,52 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>71378048</v>
+        <v>110048866</v>
       </c>
       <c r="B6" t="n">
-        <v>56887</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57945</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>102995</v>
+        <v>100110</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Buskskvätta</t>
+          <t>Gråspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Saxicola rubetra</t>
+          <t>Picus canus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>J.F. Gmelin, 1788</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Kvarnberget, SCA-rågången, Nb</t>
+          <t>Kvarnberget, Nb</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>800889.3669259243</v>
+        <v>800692</v>
       </c>
       <c r="R6" t="n">
-        <v>7329176.325592783</v>
+        <v>7329114</v>
       </c>
       <c r="S6" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1255,22 +1209,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2018-05-17</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>18:00</t>
+          <t>2022-10-12</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2018-05-17</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>19:40</t>
+          <t>2022-10-12</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1285,27 +1229,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Mats Bergquist</t>
+          <t>Robert Sandberg</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Mats Bergquist</t>
+          <t>Jonas Nordenström</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>78060043</v>
+        <v>71378048</v>
       </c>
       <c r="B7" t="n">
-        <v>93868</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58463</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1313,38 +1252,45 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2869</v>
+        <v>102995</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Buskskvätta</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Saxicola rubetra</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Girg.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Kvarnberget, SCA-rågången, Nb</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>800889.3669259243</v>
+        <v>800889</v>
       </c>
       <c r="R7" t="n">
-        <v>7329176.325592783</v>
+        <v>7329176</v>
       </c>
       <c r="S7" t="n">
         <v>50</v>
@@ -1371,27 +1317,22 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2019-05-27</t>
+          <t>2018-05-17</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2019-05-27</t>
+          <t>2018-05-17</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>17:20</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Spridd förekomst.</t>
+          <t>19:40</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1400,7 +1341,6 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1419,53 +1359,56 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>78057661</v>
+        <v>71378043</v>
       </c>
       <c r="B8" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58327</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1202</v>
+        <v>103015</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Kvarnberget, SCA-rågången, Nb</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>800889.3669259243</v>
+        <v>800889</v>
       </c>
       <c r="R8" t="n">
-        <v>7329176.325592783</v>
+        <v>7329176</v>
       </c>
       <c r="S8" t="n">
         <v>50</v>
@@ -1492,22 +1435,22 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2019-05-27</t>
+          <t>2018-05-17</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2019-05-27</t>
+          <t>2018-05-17</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>19:40</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1516,7 +1459,6 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1538,16 +1480,11 @@
         <v>78057721</v>
       </c>
       <c r="B9" t="n">
-        <v>56859</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58439</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
@@ -1587,10 +1524,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>800889.3669259243</v>
+        <v>800889</v>
       </c>
       <c r="R9" t="n">
-        <v>7329176.325592783</v>
+        <v>7329176</v>
       </c>
       <c r="S9" t="n">
         <v>50</v>
@@ -1659,15 +1596,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>81692580</v>
+        <v>53319591</v>
       </c>
       <c r="B10" t="n">
-        <v>95519</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>58656</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1675,38 +1607,45 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>221945</v>
+        <v>103056</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Videsparv</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Emberiza rustica</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
+          <t>Pallas, 1776</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Kvarnberget, SCA-rågången, Nb</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>800889.3669259243</v>
+        <v>800889</v>
       </c>
       <c r="R10" t="n">
-        <v>7329176.325592783</v>
+        <v>7329176</v>
       </c>
       <c r="S10" t="n">
         <v>50</v>
@@ -1733,22 +1672,27 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2020-01-11</t>
+          <t>2015-05-10</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2020-01-11</t>
+          <t>2015-05-10</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>På Buddbymarken.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1757,7 +1701,6 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1773,6 +1716,116 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>71377982</v>
+      </c>
+      <c r="B11" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Kvarnberget, SCA-rågången, Nb</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>800889</v>
+      </c>
+      <c r="R11" t="n">
+        <v>7329176</v>
+      </c>
+      <c r="S11" t="n">
+        <v>50</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Boden</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Överluleå</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2018-05-17</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2018-05-17</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>19:40</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Mats Bergquist</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Mats Bergquist</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 55316-2023 artfynd.xlsx
+++ b/artfynd/A 55316-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY11"/>
+  <dimension ref="A1:AZ11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -783,6 +788,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/78057661</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -898,6 +908,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/71377973</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1015,6 +1030,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/78060043</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1137,6 +1157,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/53319415</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1238,6 +1263,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110048866</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1356,6 +1386,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/71378048</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1474,6 +1509,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/71378043</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1593,6 +1633,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/78057721</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1716,6 +1761,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/53319591</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1826,8 +1876,25 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/71377982</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>